--- a/backend/static/templates/Corporate_Partners_Template.xlsx
+++ b/backend/static/templates/Corporate_Partners_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Corporate Partner Template" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indurstry" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Political Risk" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="AML Risk" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="Partner Type Ref" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Partner Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partner Types" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Political Risk" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AML Risk" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +37,6 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -49,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,9 +62,10 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,7 +74,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -442,24 +442,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,35 +506,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Company_Incorporation</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Contact_Person</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Contact_Person_Phone</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Contact_Person_Email</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Physical_Address</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Postal_Address</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Political_Risk</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>AML_Risk</t>
         </is>
@@ -541,16 +547,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Partner Type" error="Please select a valid Partner Type." promptTitle="Partner Type" prompt="Select Partner Type" type="list">
-      <formula1>'Partner Type Ref'!$B$2:$B$2</formula1>
+    <dataValidation sqref="A2:A101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid Entry" error="Please select a valid value from the dropdown." promptTitle="Dropdown" prompt="Select from dropdown" type="list">
+      <formula1>'Partner Types'!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Industry" error="Please select a valid Industry." promptTitle="Industry" prompt="Select Industry" type="list">
-      <formula1>'Indurstry'!$B$2:$B$31</formula1>
+    <dataValidation sqref="G2:G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select a valid value from the dropdown." promptTitle="Dropdown" prompt="Select from dropdown" type="list">
+      <formula1>'Industry'!$B$2:$B$31</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Political Risk" error="Please select a valid Political Risk." promptTitle="Political Risk" prompt="Select Political Risk" type="list">
+    <dataValidation sqref="O2:O101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select a valid value from the dropdown." promptTitle="Dropdown" prompt="Select from dropdown" type="list">
       <formula1>'Political Risk'!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid AML Risk" error="Please select a valid AML Risk." promptTitle="AML Risk" prompt="Select AML Risk" type="list">
+    <dataValidation sqref="P2:P101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select a valid value from the dropdown." promptTitle="Dropdown" prompt="Select from dropdown" type="list">
       <formula1>'AML Risk'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -564,227 +570,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B31"/>
+  <dimension ref="B1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Indurstry</t>
+          <t>Partner Types</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>INDIVIDUAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Pharmaceuticals</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Financial Services &amp; Banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Consumer Goods &amp; Retail</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Energy &amp; Utilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Manufacturing &amp; Industrial</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Telecommunications</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Real Estate &amp; Construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Media &amp; Entertainment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Automotive</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Agriculture &amp; Food Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hospitality &amp; Tourism</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Education &amp; Training</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Professional Services &amp; Consulting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Mining &amp; Metals</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Textiles &amp; Apparel</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Environmental Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>E-commerce</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Renewable Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence &amp; Machine Learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Fintech</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Life Sciences</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Oil &amp; Gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Consumer Electronics</t>
+          <t>CORPORATE</t>
         </is>
       </c>
     </row>
@@ -799,45 +605,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B5"/>
+  <dimension ref="B1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Industry</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Healthcare &amp; Pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Financial Services &amp; Banking</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>Consumer Goods &amp; Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Energy &amp; Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Manufacturing &amp; Industrial</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Real Estate &amp; Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Media &amp; Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Food Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hospitality &amp; Tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Education &amp; Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Professional Services &amp; Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mining &amp; Metals</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Textiles &amp; Apparel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Environmental Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Renewable Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence &amp; Machine Learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Life Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Consumer Electronics</t>
         </is>
       </c>
     </row>
@@ -852,17 +836,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B4"/>
+  <dimension ref="B1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AML Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
     </row>
@@ -884,6 +864,13 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PEP</t>
         </is>
       </c>
     </row>
@@ -898,17 +885,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B2"/>
+  <dimension ref="B1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>AML Risk</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>CORPORATE</t>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
